--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ece5360b24f418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R958c8a2355b04802"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R958c8a2355b04802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R064e5c331c4e470d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R064e5c331c4e470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56a8908b97104ce3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56a8908b97104ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6cf47d0abeae4a48"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6cf47d0abeae4a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra1ec0c488fc9422b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra1ec0c488fc9422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd519b1a8083a48a4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd519b1a8083a48a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R211b448727c5411c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R211b448727c5411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R988fcb8ebe7a4130"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R988fcb8ebe7a4130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf25bf933c7774ea5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf25bf933c7774ea5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86e92c27a93846ee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86e92c27a93846ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Radb811dc2442470b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Radb811dc2442470b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raef38d48aa1d415c"/>
   </x:sheets>
 </x:workbook>
 </file>
